--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260831.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,003,822</t>
+          <t>809,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>809,897</t>
+          <t>1,003,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>202609WTEU6F</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>376,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>202609WTEU6F</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>376,000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>10,615,121</t>
+          <t>7,178,249</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,178,249</t>
+          <t>10,615,121</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,187,076</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>1,187,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>4,966,956</t>
+          <t>805,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>805,000</t>
+          <t>4,966,956</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>291,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>291,000</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,004,121</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,760,000</t>
+          <t>1,004,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,760,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>178,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>178,000</t>
+          <t>171,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>254,000</t>
+          <t>681,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>681,000</t>
+          <t>254,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
